--- a/graduation-attainment-platform/frontend/public/templates/course-import-template.xlsx
+++ b/graduation-attainment-platform/frontend/public/templates/course-import-template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -431,20 +431,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>适用年级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>课程代码</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>课程名称</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>学分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -458,20 +463,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>CS201</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>数据结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -485,20 +495,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>CS301</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>操作系统</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
